--- a/data/trans_bre/P23_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P23_R2-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 3,68</t>
+          <t>-9,25; 3,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 5,61</t>
+          <t>-10,11; 4,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 0,49</t>
+          <t>-11,15; 0,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 3,01</t>
+          <t>-5,97; 3,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-28,22; 12,79</t>
+          <t>-28,45; 13,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 18,28</t>
+          <t>-28,35; 14,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-42,56; 2,82</t>
+          <t>-41,26; 2,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-30,97; 21,21</t>
+          <t>-31,37; 22,49</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 7,52</t>
+          <t>-6,62; 7,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 10,33</t>
+          <t>-5,66; 9,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 5,47</t>
+          <t>-7,2; 6,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 7,1</t>
+          <t>-4,22; 6,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 23,74</t>
+          <t>-17,43; 25,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 32,95</t>
+          <t>-14,94; 30,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 22,53</t>
+          <t>-23,83; 25,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 38,92</t>
+          <t>-17,28; 39,55</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-26,87; -10,32</t>
+          <t>-26,18; -10,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,74; -1,66</t>
+          <t>-15,33; -1,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,01; -0,74</t>
+          <t>-18,78; -1,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 14,45</t>
+          <t>-14,57; 11,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-56,17; -22,78</t>
+          <t>-56,58; -24,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,28; -4,16</t>
+          <t>-35,85; -3,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,97; -1,86</t>
+          <t>-43,05; -2,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-52,59; 159,16</t>
+          <t>-51,59; 130,41</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,2; -6,04</t>
+          <t>-15,65; -6,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 0,86</t>
+          <t>-8,54; 1,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 5,35</t>
+          <t>-3,85; 5,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,32; -3,82</t>
+          <t>-22,44; -3,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,25; -15,21</t>
+          <t>-35,43; -16,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,54; 2,36</t>
+          <t>-20,28; 3,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 15,48</t>
+          <t>-9,58; 16,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,52; -12,09</t>
+          <t>-66,42; -11,33</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-24,37; -11,09</t>
+          <t>-24,12; -10,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,12; -6,0</t>
+          <t>-17,23; -5,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,68; -4,12</t>
+          <t>-14,47; -4,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,97; -8,84</t>
+          <t>-21,59; -9,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-46,76; -25,19</t>
+          <t>-46,0; -24,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,74; -16,81</t>
+          <t>-39,56; -14,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-35,4; -11,54</t>
+          <t>-35,22; -12,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-58,57; -29,36</t>
+          <t>-58,08; -30,51</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,96; -8,49</t>
+          <t>-19,61; -8,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,42; -0,07</t>
+          <t>-10,26; 0,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,81; -3,38</t>
+          <t>-14,59; -3,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 5,6</t>
+          <t>-10,3; 5,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,65; -38,2</t>
+          <t>-61,22; -36,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-42,84; -0,4</t>
+          <t>-43,91; -0,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-50,36; -16,71</t>
+          <t>-49,19; -16,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-48,98; 91,79</t>
+          <t>-51,06; 97,1</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,58; -13,05</t>
+          <t>-17,61; -13,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,09; -7,53</t>
+          <t>-12,11; -7,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,86; -6,17</t>
+          <t>-10,76; -6,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,71; -0,95</t>
+          <t>-10,12; -1,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-42,92; -33,55</t>
+          <t>-43,03; -34,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,69; -21,03</t>
+          <t>-31,93; -20,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-30,29; -18,42</t>
+          <t>-30,47; -18,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-37,75; -6,93</t>
+          <t>-38,99; -6,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P23_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P23_R2-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>-2,14</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-7,99%</t>
+          <t>-12,51%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 3,81</t>
+          <t>-9,67; 3,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 4,36</t>
+          <t>-9,96; 4,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 0,55</t>
+          <t>-11,53; 0,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 3,26</t>
+          <t>-6,75; 2,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 13,71</t>
+          <t>-28,08; 12,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,35; 14,83</t>
+          <t>-27,93; 15,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-41,26; 2,41</t>
+          <t>-41,98; 1,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-31,37; 22,49</t>
+          <t>-34,11; 15,78</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>2,24</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 7,67</t>
+          <t>-6,69; 7,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 9,48</t>
+          <t>-4,79; 8,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 6,31</t>
+          <t>-7,58; 5,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 6,76</t>
+          <t>-3,42; 7,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,43; 25,13</t>
+          <t>-18,15; 24,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 30,63</t>
+          <t>-12,51; 29,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 25,69</t>
+          <t>-23,82; 22,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 39,55</t>
+          <t>-14,8; 45,76</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,69</t>
+          <t>-12,48</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-14,99%</t>
+          <t>-46,13%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-26,18; -10,51</t>
+          <t>-26,64; -11,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,33; -1,18</t>
+          <t>-15,59; -1,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,78; -1,08</t>
+          <t>-18,66; -0,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 11,5</t>
+          <t>-18,69; -6,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-56,58; -24,61</t>
+          <t>-56,87; -25,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,85; -3,19</t>
+          <t>-36,08; -3,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-43,05; -2,06</t>
+          <t>-42,48; -2,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-51,59; 130,41</t>
+          <t>-62,23; -24,5</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-10,79</t>
+          <t>-5,17</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-32,98%</t>
+          <t>-16,12%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,65; -6,59</t>
+          <t>-15,06; -6,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 1,29</t>
+          <t>-7,59; 1,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 5,72</t>
+          <t>-3,1; 5,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,44; -3,7</t>
+          <t>-9,44; -1,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,43; -16,11</t>
+          <t>-33,82; -15,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,28; 3,15</t>
+          <t>-18,16; 3,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 16,14</t>
+          <t>-7,82; 15,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,42; -11,33</t>
+          <t>-27,72; -3,63</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-14,6</t>
+          <t>-11,41</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-43,62%</t>
+          <t>-35,24%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-24,12; -10,97</t>
+          <t>-24,35; -11,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,23; -5,44</t>
+          <t>-16,92; -5,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,47; -4,4</t>
+          <t>-14,84; -4,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,59; -9,51</t>
+          <t>-16,82; -6,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-46,0; -24,78</t>
+          <t>-46,49; -24,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,56; -14,53</t>
+          <t>-39,89; -14,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-35,22; -12,05</t>
+          <t>-35,51; -13,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-58,08; -30,51</t>
+          <t>-46,1; -21,42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,84</t>
+          <t>-0,58</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-6,91%</t>
+          <t>-5,07%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,61; -8,34</t>
+          <t>-19,27; -8,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 0,1</t>
+          <t>-10,57; -0,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,59; -3,45</t>
+          <t>-15,1; -4,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 5,89</t>
+          <t>-8,12; 5,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,22; -36,89</t>
+          <t>-60,39; -38,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,91; -0,16</t>
+          <t>-43,67; 0,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-49,19; -16,65</t>
+          <t>-50,53; -18,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,06; 97,1</t>
+          <t>-45,69; 82,85</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-6,61</t>
+          <t>-6,89</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-27,06%</t>
+          <t>-26,61%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,61; -13,14</t>
+          <t>-17,5; -13,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,11; -7,3</t>
+          <t>-12,13; -7,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,76; -6,07</t>
+          <t>-10,63; -6,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,12; -1,1</t>
+          <t>-8,87; -4,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-43,03; -34,13</t>
+          <t>-42,81; -34,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,93; -20,52</t>
+          <t>-31,94; -21,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-30,47; -18,34</t>
+          <t>-29,71; -18,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-38,99; -6,4</t>
+          <t>-32,76; -19,06</t>
         </is>
       </c>
     </row>
